--- a/Genetic Diseases.xlsx
+++ b/Genetic Diseases.xlsx
@@ -5,16 +5,17 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/9ffda80931a57275/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Martin Shkreli - DL\models\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="5" documentId="8_{56472586-F334-44B4-9EAD-83A39411431B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{0F1846DF-588B-4F93-9734-09E6B2FD29D8}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F550C035-DEDF-474C-8456-F7415255C201}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2590" yWindow="5970" windowWidth="22360" windowHeight="12770" activeTab="1" xr2:uid="{A0A2AE90-9BB8-440D-BD9A-4EE3A3F69D88}"/>
+    <workbookView xWindow="13260" yWindow="3250" windowWidth="22360" windowHeight="16580" activeTab="2" xr2:uid="{A0A2AE90-9BB8-440D-BD9A-4EE3A3F69D88}"/>
   </bookViews>
   <sheets>
     <sheet name="Main" sheetId="1" r:id="rId1"/>
     <sheet name="Genetic Disease" sheetId="2" r:id="rId2"/>
+    <sheet name="Companies" sheetId="3" r:id="rId3"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -40,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4" uniqueCount="4">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="49" uniqueCount="45">
   <si>
     <t>Main</t>
   </si>
@@ -52,13 +53,136 @@
   </si>
   <si>
     <t>Spinal Muscular Atrophy</t>
+  </si>
+  <si>
+    <t>Osteogenesis Imperfecta</t>
+  </si>
+  <si>
+    <t>MPS I</t>
+  </si>
+  <si>
+    <t>MPS II</t>
+  </si>
+  <si>
+    <t>MPS IIIA</t>
+  </si>
+  <si>
+    <t>MPS IIIB</t>
+  </si>
+  <si>
+    <t>MPS IIIC</t>
+  </si>
+  <si>
+    <t>MPS IV</t>
+  </si>
+  <si>
+    <t>Niemann-Pick type A</t>
+  </si>
+  <si>
+    <t>Acid sphingomyelinase deficiency</t>
+  </si>
+  <si>
+    <t>SMPD1</t>
+  </si>
+  <si>
+    <t>sphingomyelin phosphodiesterase 1</t>
+  </si>
+  <si>
+    <t>acid sphingomyelinase</t>
+  </si>
+  <si>
+    <t>Protein</t>
+  </si>
+  <si>
+    <t>Other Name</t>
+  </si>
+  <si>
+    <t>Name</t>
+  </si>
+  <si>
+    <t>Gene Name</t>
+  </si>
+  <si>
+    <t>Gene Abbreviation</t>
+  </si>
+  <si>
+    <t>Protein Other Name</t>
+  </si>
+  <si>
+    <t>ASM</t>
+  </si>
+  <si>
+    <t>3.1.4.12</t>
+  </si>
+  <si>
+    <t>EC</t>
+  </si>
+  <si>
+    <t>Niemann-Pick type C</t>
+  </si>
+  <si>
+    <t>NPC1</t>
+  </si>
+  <si>
+    <t>NPC intracellular cholesterol transporter 1</t>
+  </si>
+  <si>
+    <t>Niemann-Pick type C NPC2</t>
+  </si>
+  <si>
+    <t>NPC intracellular cholesterol transporter 2</t>
+  </si>
+  <si>
+    <t>Incidence 1:</t>
+  </si>
+  <si>
+    <t>OMIM</t>
+  </si>
+  <si>
+    <t>257200, 607616</t>
+  </si>
+  <si>
+    <t>257220</t>
+  </si>
+  <si>
+    <t>607625</t>
+  </si>
+  <si>
+    <t>Xenpozyme (olipudase)</t>
+  </si>
+  <si>
+    <t>Drugs</t>
+  </si>
+  <si>
+    <t>Orkambi</t>
+  </si>
+  <si>
+    <t>Notes</t>
+  </si>
+  <si>
+    <t>AA</t>
+  </si>
+  <si>
+    <t>Azafaros</t>
+  </si>
+  <si>
+    <t>Biomarin</t>
+  </si>
+  <si>
+    <t>Ultragenyx</t>
+  </si>
+  <si>
+    <t>Travere</t>
+  </si>
+  <si>
+    <t>Alnylam</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -71,6 +195,14 @@
       <color theme="1"/>
       <name val="Arial"/>
       <family val="2"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color theme="10"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="2">
@@ -90,14 +222,19 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="3" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1"/>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
+    <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
@@ -439,34 +576,234 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1D4D0202-2143-4A58-965E-8A0690978F31}">
-  <dimension ref="A1:B5"/>
+  <dimension ref="A1:M15"/>
   <sheetFormatPr defaultRowHeight="12.5" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="4.6328125" style="1" bestFit="1" customWidth="1"/>
-    <col min="2" max="16384" width="8.7265625" style="1"/>
+    <col min="2" max="2" width="21.26953125" style="1" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="11.08984375" style="1" customWidth="1"/>
+    <col min="4" max="16384" width="8.7265625" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="B2" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="D2" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="E2" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="F2" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="G2" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="H2" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="I2" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="J2" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="K2" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="L2" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="M2" s="1" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="3" spans="1:13" x14ac:dyDescent="0.25">
       <c r="B3" s="1" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="K3" s="1" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="4" spans="1:13" x14ac:dyDescent="0.25">
       <c r="B4" s="1" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:13" x14ac:dyDescent="0.25">
       <c r="B5" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="6" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="B6" s="1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="7" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="B7" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="8" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="B8" s="1" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="9" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="B9" s="1" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="10" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="B10" s="1" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="11" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="B11" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="C11" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="D11" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="E11" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="F11" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="G11" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="H11" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="I11" s="2">
+        <v>100000</v>
+      </c>
+      <c r="J11" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="K11" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="M11" s="1">
+        <v>1278</v>
+      </c>
+    </row>
+    <row r="12" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="B12" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="D12" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="E12" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="F12" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="I12" s="2">
+        <v>100000</v>
+      </c>
+      <c r="J12" s="3" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="13" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="B13" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="D13" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="E13" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="F13" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="I13" s="2">
+        <v>100000</v>
+      </c>
+      <c r="J13" s="3" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="14" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="B14" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="15" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="B15" s="1" t="s">
         <v>3</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3E97A685-0D85-4D69-9FDD-72496CEC4B0D}">
+  <dimension ref="A1:B6"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="1" width="4.7265625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="9.6328125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A1" s="4" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="B2" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="B3" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="B4" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="B5" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="B6" t="s">
+        <v>40</v>
+      </c>
+    </row>
+  </sheetData>
+  <hyperlinks>
+    <hyperlink ref="A1" location="Main!A1" display="Main" xr:uid="{CCA902A7-E1D9-43B4-8454-13256B09484C}"/>
+  </hyperlinks>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>